--- a/MarineBoard/PCB Manufacturing Process Specification.xlsx
+++ b/MarineBoard/PCB Manufacturing Process Specification.xlsx
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Plugged vias with solder mask 阻焊塞孔</t>
+          <t>Resin filled + copper capped (POFV), all vias 全部树脂塞孔电镀填平</t>
         </is>
       </c>
       <c r="F9" s="59" t="n"/>

--- a/MarineBoard/PCB Manufacturing Process Specification.xlsx
+++ b/MarineBoard/PCB Manufacturing Process Specification.xlsx
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">L-4C13W831004A </t>
+          <t xml:space="preserve">MarineBoard-PCBWay-Gerbers.zip</t>
         </is>
       </c>
       <c r="C2" s="57" t="n"/>
